--- a/artfynd/A 27726-2026 artfynd.xlsx
+++ b/artfynd/A 27726-2026 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135023561</v>
+        <v>135349638</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,57 +798,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497839</v>
+        <v>497778</v>
       </c>
       <c r="R3" t="n">
-        <v>6622135</v>
+        <v>6622129</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,14 +864,14 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,25 +883,25 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Mosse med tall</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033868</v>
+        <v>135033893</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -939,7 +931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -949,7 +941,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -966,7 +958,7 @@
         <v>497786</v>
       </c>
       <c r="R4" t="n">
-        <v>6622130</v>
+        <v>6622129</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1013,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>Bälgroo med fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135033893</v>
+        <v>135034731</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1094,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497786</v>
+        <v>497800</v>
       </c>
       <c r="R5" t="n">
-        <v>6622129</v>
+        <v>6622134</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1129,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgroo med fjäder fr tupp</t>
+          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,67 +1163,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135034731</v>
+        <v>135349612</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497800</v>
+        <v>497778</v>
       </c>
       <c r="R6" t="n">
-        <v>6622134</v>
+        <v>6622129</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,27 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,16 +1256,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 27726-2026 artfynd.xlsx
+++ b/artfynd/A 27726-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033893</v>
+        <v>135023561</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -929,11 +929,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -946,22 +942,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497786</v>
+        <v>497839</v>
       </c>
       <c r="R4" t="n">
-        <v>6622129</v>
+        <v>6622135</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,27 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bälgroo med fjäder fr tupp</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,23 +1002,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135034731</v>
+        <v>135033893</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1086,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497800</v>
+        <v>497786</v>
       </c>
       <c r="R5" t="n">
-        <v>6622134</v>
+        <v>6622129</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1121,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1122,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
+          <t>Bälgroo med fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,60 +1154,67 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135349612</v>
+        <v>135034731</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497778</v>
+        <v>497800</v>
       </c>
       <c r="R6" t="n">
-        <v>6622129</v>
+        <v>6622134</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,12 +1238,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,73 +1269,76 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134232828</v>
+        <v>135349612</v>
       </c>
       <c r="B7" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497700</v>
+        <v>497778</v>
       </c>
       <c r="R7" t="n">
-        <v>6622159</v>
+        <v>6622129</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,27 +1362,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,23 +1378,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134232829</v>
+        <v>134232828</v>
       </c>
       <c r="B8" t="n">
         <v>5201</v>
@@ -1432,13 +1438,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497793</v>
+        <v>497700</v>
       </c>
       <c r="R8" t="n">
-        <v>6622169</v>
+        <v>6622159</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1483,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1506,6 +1512,122 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134232829</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497793</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6622169</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27726-2026 artfynd.xlsx
+++ b/artfynd/A 27726-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,10 +908,15 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135023561</v>
+        <v>135033893</v>
       </c>
       <c r="B4" t="n">
         <v>57162</v>
@@ -929,7 +944,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -942,27 +961,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497839</v>
+        <v>497786</v>
       </c>
       <c r="R4" t="n">
-        <v>6622135</v>
+        <v>6622129</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +1000,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bälgroo med fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,28 +1031,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Mosse med tall</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135033893</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135033893</v>
+        <v>135034731</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1077,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497786</v>
+        <v>497800</v>
       </c>
       <c r="R5" t="n">
-        <v>6622129</v>
+        <v>6622134</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1112,7 +1141,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,12 +1151,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bälgroo med fjäder fr tupp</t>
+          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,70 +1180,68 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135034731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135034731</v>
+        <v>135349612</v>
       </c>
       <c r="B6" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497800</v>
+        <v>497778</v>
       </c>
       <c r="R6" t="n">
-        <v>6622134</v>
+        <v>6622129</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,27 +1265,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,76 +1281,78 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349612</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135349612</v>
+        <v>134232828</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>5201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>slöjdarkullen, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497778</v>
+        <v>497700</v>
       </c>
       <c r="R7" t="n">
-        <v>6622129</v>
+        <v>6622159</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,12 +1376,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,28 +1407,28 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232828</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134232828</v>
+        <v>134232829</v>
       </c>
       <c r="B8" t="n">
         <v>5201</v>
@@ -1438,13 +1467,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497700</v>
+        <v>497793</v>
       </c>
       <c r="R8" t="n">
-        <v>6622159</v>
+        <v>6622169</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1512,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1512,124 +1541,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>134232829</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5201</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Gullblanka, Vstm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>497793</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6622169</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Lindesberg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232829</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27726-2026 artfynd.xlsx
+++ b/artfynd/A 27726-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135034222</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135349638</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033893</v>
+        <v>135023561</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,11 +944,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -961,22 +957,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497786</v>
+        <v>497839</v>
       </c>
       <c r="R4" t="n">
-        <v>6622129</v>
+        <v>6622135</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,27 +1001,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bälgroo med fjäder fr tupp</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,31 +1017,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033893</t>
+          <t>https://artportalen.se/Sighting/135023561</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135034731</v>
+        <v>135033893</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497800</v>
+        <v>497786</v>
       </c>
       <c r="R5" t="n">
-        <v>6622134</v>
+        <v>6622129</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1141,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1151,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
+          <t>Bälgroo med fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,66 +1173,73 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135034731</t>
+          <t>https://artportalen.se/Sighting/135033893</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135349612</v>
+        <v>135034731</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>slöjdarkullen, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497778</v>
+        <v>497800</v>
       </c>
       <c r="R6" t="n">
-        <v>6622129</v>
+        <v>6622134</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,12 +1263,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,78 +1294,81 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135349612</t>
+          <t>https://artportalen.se/Sighting/135034731</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134232828</v>
+        <v>135349612</v>
       </c>
       <c r="B7" t="n">
-        <v>5201</v>
+        <v>58141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497700</v>
+        <v>497778</v>
       </c>
       <c r="R7" t="n">
-        <v>6622159</v>
+        <v>6622129</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,27 +1392,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,28 +1408,33 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232828</t>
+          <t>https://artportalen.se/Sighting/135349612</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134232829</v>
+        <v>134232828</v>
       </c>
       <c r="B8" t="n">
         <v>5201</v>
@@ -1467,13 +1473,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497793</v>
+        <v>497700</v>
       </c>
       <c r="R8" t="n">
-        <v>6622169</v>
+        <v>6622159</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1502,7 +1508,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1518,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1542,6 +1548,127 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232828</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134232829</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497793</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6622169</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134232829</t>
         </is>
@@ -1556,6 +1683,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27726-2026 artfynd.xlsx
+++ b/artfynd/A 27726-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135023561</v>
+        <v>135349638</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,57 +808,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497839</v>
+        <v>497778</v>
       </c>
       <c r="R3" t="n">
-        <v>6622135</v>
+        <v>6622129</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,14 +874,14 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,30 +893,30 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Mosse med tall</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135023561</t>
+          <t>https://artportalen.se/Sighting/135349638</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135033893</v>
+        <v>135023561</v>
       </c>
       <c r="B4" t="n">
         <v>57167</v>
@@ -952,11 +944,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -969,22 +957,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
+          <t>Bergslagsleden, Bergslagsleden, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497786</v>
+        <v>497839</v>
       </c>
       <c r="R4" t="n">
-        <v>6622129</v>
+        <v>6622135</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,27 +1001,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bälgroo med fjäder fr tupp</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,28 +1017,33 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Mosse med tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Bengt Evertsson, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135033893</t>
+          <t>https://artportalen.se/Sighting/135023561</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135034731</v>
+        <v>135033893</v>
       </c>
       <c r="B5" t="n">
         <v>57167</v>
@@ -1114,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497800</v>
+        <v>497786</v>
       </c>
       <c r="R5" t="n">
-        <v>6622134</v>
+        <v>6622129</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1149,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
+          <t>Bälgroo med fjäder fr tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,16 +1173,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135034731</t>
+          <t>https://artportalen.se/Sighting/135033893</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134232828</v>
+        <v>135034731</v>
       </c>
       <c r="B6" t="n">
-        <v>5201</v>
+        <v>57167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,21 +1190,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1229,19 +1212,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Slöjdarkullen, Slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497700</v>
+        <v>497800</v>
       </c>
       <c r="R6" t="n">
-        <v>6622159</v>
+        <v>6622134</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,27 +1263,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Färsk och äldre spillnig. Fjädrar fr tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,69 +1298,77 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134232828</t>
+          <t>https://artportalen.se/Sighting/135034731</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134232829</v>
+        <v>135349612</v>
       </c>
       <c r="B7" t="n">
-        <v>5201</v>
+        <v>58141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>slöjdarkullen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497793</v>
+        <v>497778</v>
       </c>
       <c r="R7" t="n">
-        <v>6622169</v>
+        <v>6622129</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1386,27 +1392,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,20 +1408,267 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349612</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134232828</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>497700</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6622159</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232828</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134232829</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>497793</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6622169</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134232829</t>
         </is>
@@ -1444,6 +1682,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
